--- a/tts_envs/data/tokens.xlsx
+++ b/tts_envs/data/tokens.xlsx
@@ -11880,7 +11880,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C15"/>
+  <dimension ref="A1:D15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -11904,6 +11904,11 @@
           <t>default_rep</t>
         </is>
       </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>short</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -11919,6 +11924,11 @@
       <c r="C2" t="n">
         <v>0</v>
       </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Denizen</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -11934,6 +11944,11 @@
       <c r="C3" t="n">
         <v>0</v>
       </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Marquisate</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -11949,6 +11964,11 @@
       <c r="C4" t="n">
         <v>0</v>
       </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Dynasty</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -11964,6 +11984,11 @@
       <c r="C5" t="n">
         <v>0</v>
       </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Company</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -11979,6 +12004,11 @@
       <c r="C6" t="n">
         <v>0</v>
       </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Duchy</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -11994,6 +12024,11 @@
       <c r="C7" t="n">
         <v>-30</v>
       </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Alliance</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -12009,6 +12044,11 @@
       <c r="C8" t="n">
         <v>-30</v>
       </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Keepers</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -12024,6 +12064,11 @@
       <c r="C9" t="n">
         <v>0</v>
       </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Cult</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -12039,6 +12084,11 @@
       <c r="C10" t="n">
         <v>-30</v>
       </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Conspiracy</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -12054,6 +12104,11 @@
       <c r="C11" t="n">
         <v>-30</v>
       </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Hundreds</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -12069,6 +12124,11 @@
       <c r="C12" t="n">
         <v>-30</v>
       </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Knaves</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -12084,6 +12144,11 @@
       <c r="C13" t="n">
         <v>-30</v>
       </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Diaspora</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -12099,6 +12164,11 @@
       <c r="C14" t="n">
         <v>0</v>
       </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Council</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -12113,6 +12183,11 @@
       </c>
       <c r="C15" t="n">
         <v>30</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Guild</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/tts_envs/data/tokens.xlsx
+++ b/tts_envs/data/tokens.xlsx
@@ -5045,12 +5045,27 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>token_template</t>
+          <t>generic_meeple_template</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
           <t>token</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>custom</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>guild WA Bird</t>
+        </is>
+      </c>
+      <c r="Q120" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/cdenq/tts-roam-mod/main/assets/meeples/custom/guild_wa_bird.png</t>
         </is>
       </c>
     </row>
@@ -5062,12 +5077,27 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>token_template</t>
+          <t>generic_meeple_template</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
           <t>token</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>custom</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>guild WA Fox</t>
+        </is>
+      </c>
+      <c r="Q121" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/cdenq/tts-roam-mod/main/assets/meeples/custom/guild_wa_fox.png</t>
         </is>
       </c>
     </row>
@@ -5079,12 +5109,27 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>token_template</t>
+          <t>generic_meeple_template</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
           <t>token</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>custom</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>guild WA Mouse</t>
+        </is>
+      </c>
+      <c r="Q122" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/cdenq/tts-roam-mod/main/assets/meeples/custom/guild_wa_mouse.png</t>
         </is>
       </c>
     </row>
@@ -5096,12 +5141,27 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>token_template</t>
+          <t>generic_meeple_template</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
           <t>token</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>custom</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>guild WA Rabbit</t>
+        </is>
+      </c>
+      <c r="Q123" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/cdenq/tts-roam-mod/main/assets/meeples/custom/guild_wa_rabbit.png</t>
         </is>
       </c>
     </row>
@@ -5113,12 +5173,27 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>token_template</t>
+          <t>generic_meeple_template</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
           <t>token</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>special</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>guild Guildmaster</t>
+        </is>
+      </c>
+      <c r="Q124" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/cdenq/tts-roam-mod/main/assets/meeples/special/special_guildmaster_guild.png</t>
         </is>
       </c>
     </row>
@@ -10803,7 +10878,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J31"/>
+  <dimension ref="A1:J52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -11781,7 +11856,7 @@
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/cdenq/tts-roam-mod/main/assets/landmarks/stone_tower_s1.png?v=2</t>
+          <t>https://raw.githubusercontent.com/cdenq/tts-roam-mod/main/assets/landmarks/guild_tower_s1.png?v=1</t>
         </is>
       </c>
     </row>
@@ -11816,7 +11891,7 @@
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/cdenq/tts-roam-mod/main/assets/landmarks/stone_tower_s2.png?v=2</t>
+          <t>https://raw.githubusercontent.com/cdenq/tts-roam-mod/main/assets/landmarks/guild_tower_s2.png?v=1</t>
         </is>
       </c>
     </row>
@@ -11851,7 +11926,7 @@
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/cdenq/tts-roam-mod/main/assets/landmarks/stone_tower_s3.png?v=2</t>
+          <t>https://raw.githubusercontent.com/cdenq/tts-roam-mod/main/assets/landmarks/guild_tower_s3.png?v=1</t>
         </is>
       </c>
     </row>
@@ -11886,7 +11961,7 @@
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/cdenq/tts-roam-mod/main/assets/landmarks/stone_tower_s4.png?v=2</t>
+          <t>https://raw.githubusercontent.com/cdenq/tts-roam-mod/main/assets/landmarks/guild_tower_s4.png?v=1</t>
         </is>
       </c>
     </row>
@@ -11911,6 +11986,19 @@
           <t>landmarks</t>
         </is>
       </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Caravan</t>
+        </is>
+      </c>
+      <c r="G30" t="n">
+        <v>0</v>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/cdenq/tts-roam-mod/main/assets/landmarks/caravan_s1.png?v=1</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -11929,6 +12017,805 @@
         </is>
       </c>
       <c r="D31" t="inlineStr">
+        <is>
+          <t>landmarks</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Beehive</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/cdenq/tts-roam-mod/main/assets/landmarks/beehive_s1.png?v=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>LM31</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>landmark_template</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>token</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>landmarks</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Shrine</t>
+        </is>
+      </c>
+      <c r="G32" t="n">
+        <v>0</v>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/cdenq/tts-roam-mod/main/assets/landmarks/shrine_s1.png?v=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>LM32</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>landmark_template</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>token</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>landmarks</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Warehouse</t>
+        </is>
+      </c>
+      <c r="G33" t="n">
+        <v>1</v>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/cdenq/tts-roam-mod/main/assets/landmarks/warehouse_s1.png?v=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>LM33</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>landmark_template</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>token</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>landmarks</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Bank</t>
+        </is>
+      </c>
+      <c r="G34" t="n">
+        <v>1</v>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/cdenq/tts-roam-mod/main/assets/landmarks/bank_s1.png?v=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>LM34</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>landmark_template</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>token</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>landmarks</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Eyrie Perch</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>eyrie</t>
+        </is>
+      </c>
+      <c r="G35" t="n">
+        <v>0</v>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/cdenq/tts-roam-mod/main/assets/landmarks/eyrie_tower_s1.png?v=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>LM35</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>landmark_template</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>token</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>landmarks</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Eyrie Lookout</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>eyrie</t>
+        </is>
+      </c>
+      <c r="G36" t="n">
+        <v>1</v>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/cdenq/tts-roam-mod/main/assets/landmarks/eyrie_tower_s2.png?v=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>LM36</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>landmark_template</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>token</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>landmarks</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Eyrie Tower</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>eyrie</t>
+        </is>
+      </c>
+      <c r="G37" t="n">
+        <v>2</v>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/cdenq/tts-roam-mod/main/assets/landmarks/eyrie_tower_s3.png?v=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>LM37</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>landmark_template</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>token</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>landmarks</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Eyrie Spire</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>eyrie</t>
+        </is>
+      </c>
+      <c r="G38" t="n">
+        <v>3</v>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/cdenq/tts-roam-mod/main/assets/landmarks/eyrie_tower_s4.png?v=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>LM38</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>landmark_template</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>token</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>landmarks</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Marquise Guardhouse</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>marquisate</t>
+        </is>
+      </c>
+      <c r="G39" t="n">
+        <v>0</v>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/cdenq/tts-roam-mod/main/assets/landmarks/marquise_barracks_s1.png?v=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>LM39</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>landmark_template</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>token</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>landmarks</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>Marquise Barracks</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>marquisate</t>
+        </is>
+      </c>
+      <c r="G40" t="n">
+        <v>1</v>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/cdenq/tts-roam-mod/main/assets/landmarks/marquise_barracks_s2.png?v=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>LM40</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>landmark_template</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>token</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>landmarks</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Marquise Garrison</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>marquisate</t>
+        </is>
+      </c>
+      <c r="G41" t="n">
+        <v>2</v>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/cdenq/tts-roam-mod/main/assets/landmarks/marquise_barracks_s3.png?v=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>LM41</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>landmark_template</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>token</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>landmarks</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>Marquise Fort</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>marquisate</t>
+        </is>
+      </c>
+      <c r="G42" t="n">
+        <v>3</v>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/cdenq/tts-roam-mod/main/assets/landmarks/marquise_barracks_s4.png?v=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>LM42</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>landmark_template</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>token</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>landmarks</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>Alliance Cache</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>alliance</t>
+        </is>
+      </c>
+      <c r="G43" t="n">
+        <v>0</v>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/cdenq/tts-roam-mod/main/assets/landmarks/alliance_barracks_s1.png?v=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>LM43</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>landmark_template</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>token</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>landmarks</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>Alliance Dugout</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>alliance</t>
+        </is>
+      </c>
+      <c r="G44" t="n">
+        <v>1</v>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/cdenq/tts-roam-mod/main/assets/landmarks/alliance_barracks_s2.png?v=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>LM44</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>landmark_template</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>token</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>landmarks</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>Alliance Hideout</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>alliance</t>
+        </is>
+      </c>
+      <c r="G45" t="n">
+        <v>2</v>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/cdenq/tts-roam-mod/main/assets/landmarks/alliance_barracks_s3.png?v=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>LM45</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>landmark_template</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>token</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>landmarks</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>Alliance Stronghold</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>alliance</t>
+        </is>
+      </c>
+      <c r="G46" t="n">
+        <v>3</v>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/cdenq/tts-roam-mod/main/assets/landmarks/alliance_barracks_s4.png?v=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>LM46</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>landmark_template</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>token</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>landmarks</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>Otter Kiosk</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>riverfolk</t>
+        </is>
+      </c>
+      <c r="G47" t="n">
+        <v>0</v>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/cdenq/tts-roam-mod/main/assets/landmarks/otter_barracks_s1.png?v=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>LM47</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>landmark_template</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>token</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>landmarks</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>Otter Pavilion</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>riverfolk</t>
+        </is>
+      </c>
+      <c r="G48" t="n">
+        <v>1</v>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/cdenq/tts-roam-mod/main/assets/landmarks/otter_barracks_s2.png?v=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>LM48</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>landmark_template</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>token</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>landmarks</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>Otter Exchange</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>riverfolk</t>
+        </is>
+      </c>
+      <c r="G49" t="n">
+        <v>2</v>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/cdenq/tts-roam-mod/main/assets/landmarks/otter_barracks_s3.png?v=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>LM49</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>landmark_template</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>token</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>landmarks</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>Otter Company Hall</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>riverfolk</t>
+        </is>
+      </c>
+      <c r="G50" t="n">
+        <v>3</v>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/cdenq/tts-roam-mod/main/assets/landmarks/otter_barracks_s4.png?v=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>LM50</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>landmark_template</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>token</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>landmarks</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>LM51</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>landmark_template</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>token</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
         <is>
           <t>landmarks</t>
         </is>

--- a/tts_envs/data/tokens.xlsx
+++ b/tts_envs/data/tokens.xlsx
@@ -5205,12 +5205,32 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>token_template</t>
+          <t>enemy_meeple_template</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
           <t>token</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>enemies</t>
+        </is>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>enemy Ant</t>
+        </is>
+      </c>
+      <c r="H125" t="inlineStr">
+        <is>
+          <t>enemy</t>
+        </is>
+      </c>
+      <c r="Q125" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/cdenq/tts-roam-mod/main/assets/meeples/enemies/enemy_ant.png</t>
         </is>
       </c>
     </row>
@@ -5222,12 +5242,32 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>token_template</t>
+          <t>enemy_meeple_template</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
           <t>token</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>enemies</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>enemy Stag Beetle</t>
+        </is>
+      </c>
+      <c r="H126" t="inlineStr">
+        <is>
+          <t>enemy</t>
+        </is>
+      </c>
+      <c r="Q126" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/cdenq/tts-roam-mod/main/assets/meeples/enemies/enemy_stagbeetle.png</t>
         </is>
       </c>
     </row>
@@ -5239,12 +5279,32 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>token_template</t>
+          <t>enemy_meeple_template</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
           <t>token</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>enemies</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>enemy Spider</t>
+        </is>
+      </c>
+      <c r="H127" t="inlineStr">
+        <is>
+          <t>enemy</t>
+        </is>
+      </c>
+      <c r="Q127" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/cdenq/tts-roam-mod/main/assets/meeples/enemies/enemy_spider.png</t>
         </is>
       </c>
     </row>
@@ -5256,12 +5316,32 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>token_template</t>
+          <t>enemy_meeple_template</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
           <t>token</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>enemies</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>enemy Scorpion</t>
+        </is>
+      </c>
+      <c r="H128" t="inlineStr">
+        <is>
+          <t>enemy</t>
+        </is>
+      </c>
+      <c r="Q128" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/cdenq/tts-roam-mod/main/assets/meeples/enemies/enemy_scorpion.png</t>
         </is>
       </c>
     </row>
@@ -5273,12 +5353,32 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>token_template</t>
+          <t>enemy_meeple_template</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
           <t>token</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>enemies</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>enemy Mantis</t>
+        </is>
+      </c>
+      <c r="H129" t="inlineStr">
+        <is>
+          <t>enemy</t>
+        </is>
+      </c>
+      <c r="Q129" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/cdenq/tts-roam-mod/main/assets/meeples/enemies/enemy_mantis.png</t>
         </is>
       </c>
     </row>
@@ -5290,12 +5390,32 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>token_template</t>
+          <t>enemy_meeple_template</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
           <t>token</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>enemies</t>
+        </is>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>enemy Antlion</t>
+        </is>
+      </c>
+      <c r="H130" t="inlineStr">
+        <is>
+          <t>enemy</t>
+        </is>
+      </c>
+      <c r="Q130" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/cdenq/tts-roam-mod/main/assets/meeples/enemies/enemy_antlion.png</t>
         </is>
       </c>
     </row>
@@ -5307,12 +5427,32 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>token_template</t>
+          <t>enemy_meeple_template</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
           <t>token</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>enemies</t>
+        </is>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>enemy Wasp</t>
+        </is>
+      </c>
+      <c r="H131" t="inlineStr">
+        <is>
+          <t>enemy</t>
+        </is>
+      </c>
+      <c r="Q131" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/cdenq/tts-roam-mod/main/assets/meeples/enemies/enemy_wasp.png</t>
         </is>
       </c>
     </row>
@@ -5324,12 +5464,32 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>token_template</t>
+          <t>enemy_meeple_template</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
           <t>token</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>enemies</t>
+        </is>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>enemy Mosquito</t>
+        </is>
+      </c>
+      <c r="H132" t="inlineStr">
+        <is>
+          <t>enemy</t>
+        </is>
+      </c>
+      <c r="Q132" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/cdenq/tts-roam-mod/main/assets/meeples/enemies/enemy_mosquito.png</t>
         </is>
       </c>
     </row>
